--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11.09.2026 20:53:48</t>
+          <t>14.09.2026 20:53:52</t>
         </is>
       </c>
     </row>
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1044,26 +1044,26 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>0.23</v>
+        <v>-2.07</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P6" t="n">
         <v>440.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="R6" t="n">
         <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-2.07</v>
       </c>
       <c r="T6" t="n">
         <v>14505.48</v>
@@ -1117,26 +1117,26 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>20</v>
+        <v>19.7</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
         <v>20</v>
       </c>
       <c r="Q7" t="n">
-        <v>20</v>
+        <v>19.52</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-2.4</v>
       </c>
       <c r="T7" t="n">
         <v>14467.25</v>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14.09.2026 20:53:52</t>
+          <t>15.09.2026 20:54:00</t>
         </is>
       </c>
     </row>
@@ -1044,26 +1044,26 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>426</v>
+        <v>419.5</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>-2.07</v>
+        <v>-3.56</v>
       </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P6" t="n">
         <v>440.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>426</v>
+        <v>413.75</v>
       </c>
       <c r="R6" t="n">
         <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.07</v>
+        <v>-4.89</v>
       </c>
       <c r="T6" t="n">
         <v>14505.48</v>
@@ -1117,23 +1117,23 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>19.7</v>
+        <v>20.06</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>-1.5</v>
+        <v>0.3</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P7" t="n">
-        <v>20</v>
+        <v>20.7</v>
       </c>
       <c r="Q7" t="n">
         <v>19.52</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S7" t="n">
         <v>-2.4</v>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15.09.2026 20:54:00</t>
+          <t>16.09.2026 20:54:01</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1037,33 +1037,41 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>AÇIK</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>46281.375</v>
+      </c>
+      <c r="J6" t="n">
+        <v>413.25</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
       <c r="L6" t="n">
-        <v>419.5</v>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="n">
-        <v>-3.56</v>
-      </c>
+        <v>409.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-5</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P6" t="n">
         <v>440.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>413.75</v>
+        <v>402</v>
       </c>
       <c r="R6" t="n">
         <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>-4.89</v>
+        <v>-7.59</v>
       </c>
       <c r="T6" t="n">
         <v>14505.48</v>
@@ -1110,33 +1118,41 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>AÇIK</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>46281.375</v>
+      </c>
+      <c r="J7" t="n">
+        <v>19</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>20.06</v>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="n">
-        <v>0.3</v>
-      </c>
+        <v>19.55</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P7" t="n">
         <v>20.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>19.52</v>
+        <v>18.89</v>
       </c>
       <c r="R7" t="n">
         <v>3.5</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.4</v>
+        <v>-5.55</v>
       </c>
       <c r="T7" t="n">
         <v>14467.25</v>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16.09.2026 20:54:01</t>
+          <t>17.09.2026 20:54:04</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17.09.2026 20:54:04</t>
+          <t>18.09.2026 20:53:54</t>
         </is>
       </c>
     </row>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18.09.2026 20:53:54</t>
+          <t>21.09.2026 20:53:47</t>
         </is>
       </c>
     </row>
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y7"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1166,6 +1166,79 @@
       </c>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ISLEM-000007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TUPRS</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>414.75</v>
+      </c>
+      <c r="G8" t="n">
+        <v>394.01</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>414.75</v>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>414.75</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>414.75</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>13337.69</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
         </is>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21.09.2026 20:53:47</t>
+          <t>22.09.2026 20:53:44</t>
         </is>
       </c>
     </row>
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1199,33 +1199,41 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>AÇIK</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>46287.375</v>
+      </c>
+      <c r="J8" t="n">
+        <v>394.01</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
       <c r="L8" t="n">
-        <v>414.75</v>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-5</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>414.75</v>
+        <v>424.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>414.75</v>
+        <v>389.75</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-6.03</v>
       </c>
       <c r="T8" t="n">
         <v>13337.69</v>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22.09.2026 20:53:44</t>
+          <t>23.09.2026 20:54:10</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23.09.2026 20:54:10</t>
+          <t>24.09.2026 20:53:54</t>
         </is>
       </c>
     </row>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>24.09.2026 20:53:54</t>
+          <t>25.09.2026 20:54:04</t>
         </is>
       </c>
     </row>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>25.09.2026 20:54:04</t>
+          <t>28.09.2026 20:54:17</t>
         </is>
       </c>
     </row>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>28.09.2026 20:54:17</t>
+          <t>29.09.2026 20:53:54</t>
         </is>
       </c>
     </row>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>29.09.2026 20:53:54</t>
+          <t>30.09.2026 20:53:59</t>
         </is>
       </c>
     </row>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30.09.2026 20:53:59</t>
+          <t>01.10.2026 20:54:06</t>
         </is>
       </c>
     </row>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>01.10.2026 20:54:06</t>
+          <t>02.10.2026 20:54:05</t>
         </is>
       </c>
     </row>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>02.10.2026 20:54:05</t>
+          <t>05.10.2026 20:53:55</t>
         </is>
       </c>
     </row>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>05.10.2026 20:53:55</t>
+          <t>06.10.2026 20:54:02</t>
         </is>
       </c>
     </row>
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1247,6 +1247,79 @@
       </c>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ISLEM-000008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ISDMR</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>GUCLU AL</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>61.95</v>
+      </c>
+      <c r="G9" t="n">
+        <v>58.85</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>61.95</v>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>61.95</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>61.95</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>12374.26</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
         </is>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>06.10.2026 20:54:02</t>
+          <t>07.10.2026 20:54:15</t>
         </is>
       </c>
     </row>
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -1287,26 +1287,26 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>61.95</v>
+        <v>62.2</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>61.95</v>
+        <v>63</v>
       </c>
       <c r="Q9" t="n">
-        <v>61.95</v>
+        <v>61.25</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="T9" t="n">
         <v>12374.26</v>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>07.10.2026 20:54:15</t>
+          <t>08.10.2026 20:53:56</t>
         </is>
       </c>
     </row>
@@ -1287,14 +1287,14 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>62.2</v>
+        <v>62.25</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
         <v>63</v>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>08.10.2026 20:53:56</t>
+          <t>09.10.2026 20:54:00</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
         <v>61.95</v>
       </c>
       <c r="G9" t="n">
-        <v>58.85</v>
+        <v>61.95</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1287,23 +1287,23 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>62.25</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>0.48</v>
+        <v>6.38</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>63</v>
+        <v>66.3</v>
       </c>
       <c r="Q9" t="n">
         <v>61.25</v>
       </c>
       <c r="R9" t="n">
-        <v>1.69</v>
+        <v>7.02</v>
       </c>
       <c r="S9" t="n">
         <v>-1.13</v>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09.10.2026 20:54:00</t>
+          <t>12.10.2026 20:53:53</t>
         </is>
       </c>
     </row>
@@ -1287,14 +1287,14 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>65.90000000000001</v>
+        <v>63.15</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>6.38</v>
+        <v>1.94</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P9" t="n">
         <v>66.3</v>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12.10.2026 20:53:53</t>
+          <t>13.10.2026 20:54:29</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -1280,21 +1280,29 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>AÇIK</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>46308.375</v>
+      </c>
+      <c r="J9" t="n">
+        <v>61.95</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>BASABAS (BE)</t>
+        </is>
+      </c>
       <c r="L9" t="n">
-        <v>63.15</v>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="n">
-        <v>1.94</v>
-      </c>
+        <v>62.4</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P9" t="n">
         <v>66.3</v>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13.10.2026 20:54:29</t>
+          <t>14.10.2026 20:54:01</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14.10.2026 20:54:01</t>
+          <t>15.10.2026 20:54:00</t>
         </is>
       </c>
     </row>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15.10.2026 20:54:00</t>
+          <t>16.10.2026 20:53:51</t>
         </is>
       </c>
     </row>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16.10.2026 20:53:51</t>
+          <t>19.10.2026 20:54:09</t>
         </is>
       </c>
     </row>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>19.10.2026 20:54:09</t>
+          <t>20.10.2026 20:54:03</t>
         </is>
       </c>
     </row>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20.10.2026 20:54:03</t>
+          <t>21.10.2026 20:53:56</t>
         </is>
       </c>
     </row>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21.10.2026 20:53:56</t>
+          <t>22.10.2026 20:54:05</t>
         </is>
       </c>
     </row>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22.10.2026 20:54:05</t>
+          <t>23.10.2026 20:54:07</t>
         </is>
       </c>
     </row>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23.10.2026 20:54:07</t>
+          <t>26.10.2026 20:54:09</t>
         </is>
       </c>
     </row>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>26.10.2026 20:54:09</t>
+          <t>27.10.2026 20:54:09</t>
         </is>
       </c>
     </row>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>27.10.2026 20:54:09</t>
+          <t>28.10.2026 20:54:09</t>
         </is>
       </c>
     </row>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>28.10.2026 20:54:09</t>
+          <t>29.10.2026 20:54:06</t>
         </is>
       </c>
     </row>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>29.10.2026 20:54:06</t>
+          <t>30.10.2026 20:54:18</t>
         </is>
       </c>
     </row>
